--- a/data/trans_orig/P29-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P29-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2007</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>335556</t>
+          <t>331458</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>399413</t>
+          <t>391591</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>894127</t>
+          <t>893517</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>957331</t>
+          <t>958872</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1244006</t>
+          <t>1241431</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1336278</t>
+          <t>1339723</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>174665</t>
+          <t>172929</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>223414</t>
+          <t>222454</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>193324</t>
+          <t>197272</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>247964</t>
+          <t>251219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>383356</t>
+          <t>384122</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>462070</t>
+          <t>462027</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>438458</t>
+          <t>438639</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>503183</t>
+          <t>502570</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>144739</t>
+          <t>143538</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>192890</t>
+          <t>192059</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>599175</t>
+          <t>594771</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>683549</t>
+          <t>679164</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>347586</t>
+          <t>350094</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>419434</t>
+          <t>416252</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>633618</t>
+          <t>637479</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>710636</t>
+          <t>711872</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>999433</t>
+          <t>1000565</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1106968</t>
+          <t>1107633</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>223917</t>
+          <t>225032</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>282236</t>
+          <t>283316</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>347028</t>
+          <t>347571</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>412874</t>
+          <t>414655</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>588731</t>
+          <t>590254</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>680876</t>
+          <t>676751</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1019084</t>
+          <t>1019594</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1094500</t>
+          <t>1100869</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>499155</t>
+          <t>499028</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>576031</t>
+          <t>572360</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1537696</t>
+          <t>1536753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1647732</t>
+          <t>1652048</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91309</t>
+          <t>93077</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>131438</t>
+          <t>131612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164674</t>
+          <t>166509</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>206427</t>
+          <t>207591</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>269110</t>
+          <t>266754</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>326981</t>
+          <t>323891</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,51%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73162</t>
+          <t>75541</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109629</t>
+          <t>109406</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80311</t>
+          <t>78395</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115347</t>
+          <t>115984</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162499</t>
+          <t>162247</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>210625</t>
+          <t>212942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>325404</t>
+          <t>327030</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>372723</t>
+          <t>372772</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172932</t>
+          <t>173704</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>214535</t>
+          <t>215025</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>512473</t>
+          <t>511849</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>576730</t>
+          <t>577297</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,17%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>804658</t>
+          <t>802564</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>906429</t>
+          <t>900023</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1728429</t>
+          <t>1719761</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1839822</t>
+          <t>1847016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2556065</t>
+          <t>2563608</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2716679</t>
+          <t>2717815</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>500418</t>
+          <t>503282</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>586846</t>
+          <t>587875</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>653414</t>
+          <t>649158</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>748064</t>
+          <t>746706</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1174469</t>
+          <t>1177769</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1302182</t>
+          <t>1307266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1821344</t>
+          <t>1829096</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1937089</t>
+          <t>1937077</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>844598</t>
+          <t>842806</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>949631</t>
+          <t>949667</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2705088</t>
+          <t>2701121</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2865563</t>
+          <t>2862436</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,01%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2012</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>321435</t>
+          <t>325181</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>386285</t>
+          <t>385474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>938883</t>
+          <t>934450</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1004530</t>
+          <t>1003715</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1277586</t>
+          <t>1278434</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1376152</t>
+          <t>1376650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,56%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88658</t>
+          <t>89063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>127447</t>
+          <t>129631</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113647</t>
+          <t>114446</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>156071</t>
+          <t>160016</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>216288</t>
+          <t>212348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>275861</t>
+          <t>270621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>480354</t>
+          <t>480488</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>544814</t>
+          <t>542470</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>205527</t>
+          <t>205336</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>262108</t>
+          <t>260995</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>698344</t>
+          <t>700899</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>790438</t>
+          <t>793429</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>465428</t>
+          <t>461836</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>545074</t>
+          <t>541802</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>838430</t>
+          <t>840174</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>922382</t>
+          <t>926485</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1319629</t>
+          <t>1322772</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1446444</t>
+          <t>1442885</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>233310</t>
+          <t>231541</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>294194</t>
+          <t>293702</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>246118</t>
+          <t>247977</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>307775</t>
+          <t>312929</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>497497</t>
+          <t>492803</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>586234</t>
+          <t>582528</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1153113</t>
+          <t>1156374</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1241721</t>
+          <t>1244907</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>558738</t>
+          <t>556941</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>639460</t>
+          <t>637770</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1726426</t>
+          <t>1735152</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1859456</t>
+          <t>1860760</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,0%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69519</t>
+          <t>67977</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>107820</t>
+          <t>106333</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145701</t>
+          <t>145486</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>188420</t>
+          <t>187519</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>222810</t>
+          <t>222392</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>282973</t>
+          <t>283220</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,17%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53106</t>
+          <t>52956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87142</t>
+          <t>88038</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51780</t>
+          <t>51914</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84147</t>
+          <t>83714</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112154</t>
+          <t>114207</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159798</t>
+          <t>159536</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>303801</t>
+          <t>302989</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348128</t>
+          <t>348757</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>202417</t>
+          <t>203309</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>248981</t>
+          <t>248787</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>519412</t>
+          <t>520193</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>581732</t>
+          <t>584693</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,28%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>889740</t>
+          <t>892701</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>995118</t>
+          <t>994721</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1961496</t>
+          <t>1957281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2086043</t>
+          <t>2079993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2875970</t>
+          <t>2885454</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3055153</t>
+          <t>3043663</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,66%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>399924</t>
+          <t>400738</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>480342</t>
+          <t>480048</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>432575</t>
+          <t>435292</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>515252</t>
+          <t>518978</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>856331</t>
+          <t>854981</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>973013</t>
+          <t>974104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1979161</t>
+          <t>1984251</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2095630</t>
+          <t>2098743</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>997832</t>
+          <t>1000260</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1110865</t>
+          <t>1112804</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3002148</t>
+          <t>3015293</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3182845</t>
+          <t>3186436</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2016</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2016 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95384</t>
+          <t>96186</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>137141</t>
+          <t>135812</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>481507</t>
+          <t>481876</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>547327</t>
+          <t>549569</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>591569</t>
+          <t>589161</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>674165</t>
+          <t>669801</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,41%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>254366</t>
+          <t>253517</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305117</t>
+          <t>302808</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>305954</t>
+          <t>307144</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>368816</t>
+          <t>369487</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>578163</t>
+          <t>576117</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>656588</t>
+          <t>656064</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>331728</t>
+          <t>335781</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>383842</t>
+          <t>386271</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>116525</t>
+          <t>114685</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160639</t>
+          <t>159937</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>461826</t>
+          <t>459710</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>540414</t>
+          <t>531907</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,51%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>243347</t>
+          <t>238739</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307823</t>
+          <t>308272</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>476290</t>
+          <t>475079</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>556739</t>
+          <t>561767</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>743225</t>
+          <t>741019</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>844856</t>
+          <t>843065</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>506556</t>
+          <t>503743</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>587777</t>
+          <t>584675</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>701680</t>
+          <t>698972</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>792889</t>
+          <t>786570</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1226204</t>
+          <t>1225084</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1344980</t>
+          <t>1346198</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1208354</t>
+          <t>1212456</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1299665</t>
+          <t>1305528</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>687782</t>
+          <t>684605</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>774411</t>
+          <t>772013</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1920418</t>
+          <t>1924720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2051767</t>
+          <t>2050083</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,45%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30478</t>
+          <t>30273</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56927</t>
+          <t>57254</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71001</t>
+          <t>69641</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>102978</t>
+          <t>104355</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107845</t>
+          <t>108633</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>149341</t>
+          <t>151349</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106227</t>
+          <t>105279</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>144216</t>
+          <t>144714</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>156043</t>
+          <t>155107</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>199928</t>
+          <t>199126</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>274071</t>
+          <t>273004</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>331870</t>
+          <t>330604</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>359275</t>
+          <t>357856</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>400982</t>
+          <t>401703</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>259516</t>
+          <t>260783</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>305662</t>
+          <t>309436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>630734</t>
+          <t>632743</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>694593</t>
+          <t>698429</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,85%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>392414</t>
+          <t>392540</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>472878</t>
+          <t>470715</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1064387</t>
+          <t>1062349</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1179582</t>
+          <t>1176493</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1477707</t>
+          <t>1472935</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1625441</t>
+          <t>1619668</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>892364</t>
+          <t>897972</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1001160</t>
+          <t>994115</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1197242</t>
+          <t>1201359</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1313893</t>
+          <t>1315619</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2122468</t>
+          <t>2128896</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2286657</t>
+          <t>2283816</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1941443</t>
+          <t>1941602</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2058850</t>
+          <t>2051817</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1091348</t>
+          <t>1093357</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1208582</t>
+          <t>1208106</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3057942</t>
+          <t>3061509</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3228516</t>
+          <t>3229325</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2023</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>60680</t>
+          <t>59377</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87606</t>
+          <t>87743</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>307034</t>
+          <t>307881</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>346477</t>
+          <t>348154</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>375522</t>
+          <t>375189</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>426253</t>
+          <t>427969</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>144486</t>
+          <t>144376</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>183104</t>
+          <t>183141</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>285411</t>
+          <t>287316</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>326260</t>
+          <t>327631</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>439897</t>
+          <t>441401</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>499807</t>
+          <t>496542</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>254414</t>
+          <t>254748</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>295531</t>
+          <t>296888</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101988</t>
+          <t>102839</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>133681</t>
+          <t>133463</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>363201</t>
+          <t>365520</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>421423</t>
+          <t>421513</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>228457</t>
+          <t>237029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>385041</t>
+          <t>382158</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>441413</t>
+          <t>433678</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>680429</t>
+          <t>672917</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>723744</t>
+          <t>722787</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1020825</t>
+          <t>1025852</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>355753</t>
+          <t>377971</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>607829</t>
+          <t>608750</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>465743</t>
+          <t>486625</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>745853</t>
+          <t>742811</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>940732</t>
+          <t>949750</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1312649</t>
+          <t>1315385</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1310216</t>
+          <t>1312674</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1707574</t>
+          <t>1661827</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>837066</t>
+          <t>844456</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1328602</t>
+          <t>1309472</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2211954</t>
+          <t>2214433</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2850931</t>
+          <t>2841213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,85%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83787</t>
+          <t>82113</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>120502</t>
+          <t>120194</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>142647</t>
+          <t>144019</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>179529</t>
+          <t>180477</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>236558</t>
+          <t>239104</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>287053</t>
+          <t>290255</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>113680</t>
+          <t>116864</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160498</t>
+          <t>159956</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>146484</t>
+          <t>146977</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>187870</t>
+          <t>186295</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275079</t>
+          <t>274296</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>332858</t>
+          <t>336312</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>382663</t>
+          <t>382019</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>436860</t>
+          <t>434360</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>309116</t>
+          <t>308662</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>354234</t>
+          <t>352981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>708561</t>
+          <t>708655</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>777682</t>
+          <t>775666</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,42%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>396929</t>
+          <t>385865</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>561573</t>
+          <t>556879</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>861306</t>
+          <t>848330</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1166208</t>
+          <t>1168761</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1362036</t>
+          <t>1367632</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1699212</t>
+          <t>1701472</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>636138</t>
+          <t>632361</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>915847</t>
+          <t>916444</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>923859</t>
+          <t>917255</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1209562</t>
+          <t>1216526</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1678793</t>
+          <t>1695204</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2099600</t>
+          <t>2091120</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,49%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1992506</t>
+          <t>1993004</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2423803</t>
+          <t>2445506</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1295506</t>
+          <t>1288706</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1855889</t>
+          <t>1876746</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3328599</t>
+          <t>3341959</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4060154</t>
+          <t>4031414</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,86%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P29-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P29-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>331458</t>
+          <t>333049</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>391591</t>
+          <t>393015</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>893517</t>
+          <t>894813</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>958872</t>
+          <t>957159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1241431</t>
+          <t>1241988</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1339723</t>
+          <t>1343417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,24%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172929</t>
+          <t>175690</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>222454</t>
+          <t>223532</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>197272</t>
+          <t>194459</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>251219</t>
+          <t>247399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>384122</t>
+          <t>383285</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>462027</t>
+          <t>455980</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,43%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>438639</t>
+          <t>435811</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>502570</t>
+          <t>498277</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>143538</t>
+          <t>147067</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>192059</t>
+          <t>192779</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>594771</t>
+          <t>593169</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>679164</t>
+          <t>682313</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350094</t>
+          <t>347025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>416252</t>
+          <t>416753</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>637479</t>
+          <t>636916</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>711872</t>
+          <t>713676</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1000565</t>
+          <t>1003800</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1107633</t>
+          <t>1111664</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>225032</t>
+          <t>224766</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>283316</t>
+          <t>284909</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>347571</t>
+          <t>347661</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>414655</t>
+          <t>414239</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>590254</t>
+          <t>588433</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>676751</t>
+          <t>675715</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1019594</t>
+          <t>1017110</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1100869</t>
+          <t>1098369</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>499028</t>
+          <t>495710</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>572360</t>
+          <t>569073</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1536753</t>
+          <t>1534031</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1652048</t>
+          <t>1654658</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93077</t>
+          <t>92538</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>131612</t>
+          <t>132201</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166509</t>
+          <t>163041</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>207591</t>
+          <t>207267</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>266754</t>
+          <t>266066</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>323891</t>
+          <t>328729</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75541</t>
+          <t>74841</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109406</t>
+          <t>109735</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78395</t>
+          <t>80558</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115984</t>
+          <t>114633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162247</t>
+          <t>161565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>212942</t>
+          <t>213413</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327030</t>
+          <t>326217</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>372772</t>
+          <t>373247</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173704</t>
+          <t>172195</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>215025</t>
+          <t>216036</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>511849</t>
+          <t>511327</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>577297</t>
+          <t>580411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,47%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>802564</t>
+          <t>796874</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>900023</t>
+          <t>900685</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1719761</t>
+          <t>1732032</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1847016</t>
+          <t>1841319</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2563608</t>
+          <t>2553101</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2717815</t>
+          <t>2721330</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>503282</t>
+          <t>497623</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>587875</t>
+          <t>581705</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>649158</t>
+          <t>652015</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>746706</t>
+          <t>744606</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1177769</t>
+          <t>1175969</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1307266</t>
+          <t>1307369</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1829096</t>
+          <t>1828370</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1937077</t>
+          <t>1940337</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>842806</t>
+          <t>843828</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>949667</t>
+          <t>948671</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2701121</t>
+          <t>2701679</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2862436</t>
+          <t>2867395</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>325181</t>
+          <t>321364</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>385474</t>
+          <t>386155</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>934450</t>
+          <t>939234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1003715</t>
+          <t>1008373</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1278434</t>
+          <t>1276348</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1376650</t>
+          <t>1375309</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89063</t>
+          <t>89252</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>129631</t>
+          <t>127832</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114446</t>
+          <t>112082</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>160016</t>
+          <t>154566</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>212348</t>
+          <t>213824</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>270621</t>
+          <t>272476</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>480488</t>
+          <t>479015</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>542470</t>
+          <t>547549</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>205336</t>
+          <t>200772</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>260995</t>
+          <t>260464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>700899</t>
+          <t>698027</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>793429</t>
+          <t>793919</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>461836</t>
+          <t>461003</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>541802</t>
+          <t>538374</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>840174</t>
+          <t>838473</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>926485</t>
+          <t>925886</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1322772</t>
+          <t>1322464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1442885</t>
+          <t>1452145</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>231541</t>
+          <t>235518</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>293702</t>
+          <t>295949</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247977</t>
+          <t>246026</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>312929</t>
+          <t>309728</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>492803</t>
+          <t>495553</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>582528</t>
+          <t>579414</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1156374</t>
+          <t>1158360</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1244907</t>
+          <t>1242946</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>556941</t>
+          <t>557146</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>637770</t>
+          <t>640856</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1735152</t>
+          <t>1730568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1860760</t>
+          <t>1857511</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67977</t>
+          <t>68063</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>106333</t>
+          <t>105935</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145486</t>
+          <t>145051</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>187519</t>
+          <t>189542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>222392</t>
+          <t>224407</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>283220</t>
+          <t>281563</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52956</t>
+          <t>52034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88038</t>
+          <t>86161</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51914</t>
+          <t>52641</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83714</t>
+          <t>85645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114207</t>
+          <t>114567</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>159536</t>
+          <t>161254</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>302989</t>
+          <t>304026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348757</t>
+          <t>348415</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203309</t>
+          <t>202638</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>248787</t>
+          <t>246575</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>520193</t>
+          <t>516929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>584693</t>
+          <t>584633</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,27%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>892701</t>
+          <t>888864</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>994721</t>
+          <t>1000019</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1957281</t>
+          <t>1959559</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2079993</t>
+          <t>2080887</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2885454</t>
+          <t>2873041</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3043663</t>
+          <t>3049924</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>400738</t>
+          <t>395857</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>480048</t>
+          <t>478299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>435292</t>
+          <t>437398</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>518978</t>
+          <t>517394</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>854981</t>
+          <t>861318</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>974104</t>
+          <t>977005</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1984251</t>
+          <t>1984584</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2098743</t>
+          <t>2107845</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1000260</t>
+          <t>999434</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1112804</t>
+          <t>1111561</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3015293</t>
+          <t>2997746</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3186436</t>
+          <t>3177212</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>96186</t>
+          <t>96840</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>135812</t>
+          <t>137195</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>481876</t>
+          <t>481113</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>549569</t>
+          <t>546517</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>589161</t>
+          <t>589557</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>669801</t>
+          <t>669270</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>253517</t>
+          <t>250892</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>302808</t>
+          <t>303566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307144</t>
+          <t>307777</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>369487</t>
+          <t>371273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>576117</t>
+          <t>579133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>656064</t>
+          <t>656120</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>335781</t>
+          <t>331768</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>386271</t>
+          <t>388409</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>114685</t>
+          <t>114754</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>159937</t>
+          <t>160176</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>459710</t>
+          <t>458777</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>531907</t>
+          <t>533687</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>238739</t>
+          <t>245498</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>308272</t>
+          <t>306385</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>475079</t>
+          <t>480981</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561767</t>
+          <t>560314</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>741019</t>
+          <t>740227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>843065</t>
+          <t>848790</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>503743</t>
+          <t>501606</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>584675</t>
+          <t>581850</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>698972</t>
+          <t>696714</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>786570</t>
+          <t>783471</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1225084</t>
+          <t>1225459</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1346198</t>
+          <t>1344486</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1212456</t>
+          <t>1212903</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1305528</t>
+          <t>1305029</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>684605</t>
+          <t>686870</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>772013</t>
+          <t>772394</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1924720</t>
+          <t>1916992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2050083</t>
+          <t>2051607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,49%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30273</t>
+          <t>31400</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57254</t>
+          <t>57728</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>69641</t>
+          <t>69145</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>104355</t>
+          <t>103308</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>108633</t>
+          <t>104016</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>151349</t>
+          <t>150002</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105279</t>
+          <t>105891</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>144714</t>
+          <t>144817</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155107</t>
+          <t>155300</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>199126</t>
+          <t>200200</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>273004</t>
+          <t>274301</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>330604</t>
+          <t>334524</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>357856</t>
+          <t>357060</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>401703</t>
+          <t>399760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>260783</t>
+          <t>260187</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>309436</t>
+          <t>307199</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>632743</t>
+          <t>631210</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>698429</t>
+          <t>695649</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,59%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>392540</t>
+          <t>392522</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>470715</t>
+          <t>473987</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1062349</t>
+          <t>1063555</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1176493</t>
+          <t>1178674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1472935</t>
+          <t>1482337</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1619668</t>
+          <t>1623921</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>897972</t>
+          <t>894440</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>994115</t>
+          <t>1000836</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1201359</t>
+          <t>1190917</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1315619</t>
+          <t>1308144</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2128896</t>
+          <t>2128407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2283816</t>
+          <t>2280857</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1941602</t>
+          <t>1934628</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2051817</t>
+          <t>2055400</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1093357</t>
+          <t>1097420</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1208106</t>
+          <t>1208476</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3061509</t>
+          <t>3059780</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3229325</t>
+          <t>3230773</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,82%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>73300</t>
+          <t>111875</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59377</t>
+          <t>93806</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87743</t>
+          <t>133565</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>327797</t>
+          <t>361015</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>307881</t>
+          <t>339356</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>348154</t>
+          <t>382648</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>401097</t>
+          <t>472890</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>375189</t>
+          <t>443311</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>427969</t>
+          <t>502929</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>163644</t>
+          <t>175402</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>144376</t>
+          <t>156546</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>183141</t>
+          <t>196895</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>306883</t>
+          <t>330507</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287316</t>
+          <t>310666</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>327631</t>
+          <t>353511</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>470527</t>
+          <t>505909</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>441401</t>
+          <t>475855</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>496542</t>
+          <t>537128</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>38,49%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>275795</t>
+          <t>288971</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>254748</t>
+          <t>265104</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>296888</t>
+          <t>311553</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>116653</t>
+          <t>127768</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>102839</t>
+          <t>111802</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>133463</t>
+          <t>145313</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>392448</t>
+          <t>416738</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>365520</t>
+          <t>388017</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>421513</t>
+          <t>448153</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>512739</t>
+          <t>576248</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>512739</t>
+          <t>576248</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>512739</t>
+          <t>576248</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>751333</t>
+          <t>819289</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>751333</t>
+          <t>819289</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>751333</t>
+          <t>819289</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1264072</t>
+          <t>1395537</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1264072</t>
+          <t>1395537</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1264072</t>
+          <t>1395537</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>326495</t>
+          <t>390781</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>237029</t>
+          <t>349025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>382158</t>
+          <t>429879</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>577281</t>
+          <t>633625</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>433678</t>
+          <t>597728</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>672917</t>
+          <t>672456</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>903775</t>
+          <t>1024406</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>722787</t>
+          <t>967913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1025852</t>
+          <t>1084079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>528319</t>
+          <t>567043</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>377971</t>
+          <t>521533</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>608750</t>
+          <t>616476</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>648639</t>
+          <t>720837</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>486625</t>
+          <t>684387</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>762409</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1176958</t>
+          <t>1287881</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>949750</t>
+          <t>1229180</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1315385</t>
+          <t>1346271</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>30,64%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1431521</t>
+          <t>1268649</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1312674</t>
+          <t>1217862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1661827</t>
+          <t>1325749</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1008585</t>
+          <t>813316</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>844456</t>
+          <t>770213</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1309472</t>
+          <t>856837</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2440105</t>
+          <t>2081965</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2214433</t>
+          <t>2009884</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2841213</t>
+          <t>2156209</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>49,07%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2286334</t>
+          <t>2226473</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2286334</t>
+          <t>2226473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2286334</t>
+          <t>2226473</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2234505</t>
+          <t>2167778</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2234505</t>
+          <t>2167778</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2234505</t>
+          <t>2167778</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4520838</t>
+          <t>4394251</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4520838</t>
+          <t>4394251</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4520838</t>
+          <t>4394251</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>100778</t>
+          <t>116602</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>82113</t>
+          <t>97979</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>120194</t>
+          <t>137088</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>161277</t>
+          <t>188199</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>144019</t>
+          <t>167627</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>180477</t>
+          <t>208454</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>262055</t>
+          <t>304801</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>239104</t>
+          <t>279325</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>290255</t>
+          <t>335591</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>135805</t>
+          <t>150975</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>116864</t>
+          <t>128866</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159956</t>
+          <t>175708</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>166312</t>
+          <t>182177</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>146977</t>
+          <t>161947</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>186295</t>
+          <t>204170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>302117</t>
+          <t>333152</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>274296</t>
+          <t>302356</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>336312</t>
+          <t>364925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>410040</t>
+          <t>444010</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>382019</t>
+          <t>418299</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>434360</t>
+          <t>470219</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>331179</t>
+          <t>362492</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>308662</t>
+          <t>338857</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>352981</t>
+          <t>388173</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>741219</t>
+          <t>806502</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>708655</t>
+          <t>767730</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>775666</t>
+          <t>843096</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>58,37%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>658768</t>
+          <t>732868</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>658768</t>
+          <t>732868</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>658768</t>
+          <t>732868</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1305391</t>
+          <t>1444455</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1305391</t>
+          <t>1444455</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1305391</t>
+          <t>1444455</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>500573</t>
+          <t>619258</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>385865</t>
+          <t>572148</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>556879</t>
+          <t>671571</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1066355</t>
+          <t>1182839</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>848330</t>
+          <t>1132954</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1168761</t>
+          <t>1236542</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1566927</t>
+          <t>1802097</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1367632</t>
+          <t>1725471</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1701472</t>
+          <t>1879043</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>25,97%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>827767</t>
+          <t>893420</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>632361</t>
+          <t>843344</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>916444</t>
+          <t>953789</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1121834</t>
+          <t>1233521</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>917255</t>
+          <t>1184304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1216526</t>
+          <t>1284007</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1949602</t>
+          <t>2126941</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1695204</t>
+          <t>2048520</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2091120</t>
+          <t>2212376</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2117356</t>
+          <t>2001630</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1993004</t>
+          <t>1937111</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2445506</t>
+          <t>2070684</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1456417</t>
+          <t>1303575</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1288706</t>
+          <t>1252632</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1876746</t>
+          <t>1361347</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3573773</t>
+          <t>3305205</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3341959</t>
+          <t>3221198</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4031414</t>
+          <t>3393335</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>46,91%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3445696</t>
+          <t>3514308</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3445696</t>
+          <t>3514308</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3445696</t>
+          <t>3514308</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3644606</t>
+          <t>3719935</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3644606</t>
+          <t>3719935</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3644606</t>
+          <t>3719935</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7090301</t>
+          <t>7234243</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7090301</t>
+          <t>7234243</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7090301</t>
+          <t>7234243</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
